--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2688"/>
+  <dimension ref="A1:E2690"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73004,6 +73004,60 @@
         </is>
       </c>
     </row>
+    <row r="2689">
+      <c r="A2689" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B2689" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2689" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D2689" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="E2689" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+    </row>
+    <row r="2690">
+      <c r="A2690" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B2690" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2690" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D2690" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E2690" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
